--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="114">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -330,6 +330,48 @@
   </si>
   <si>
     <t>CMX-MilpaAlta.pdv</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>CMX-Centro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chile.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Union.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Uruguay.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vallejo.pdv</t>
+  </si>
+  <si>
+    <t>IXS-IxtapanSal.pdv</t>
+  </si>
+  <si>
+    <t>SABINA</t>
+  </si>
+  <si>
+    <t>ARR-Arriaga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Alva.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Argentina.pdvc</t>
+  </si>
+  <si>
+    <t>CMX-Cuba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Febrero.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Popotla.pdv</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1516,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -2219,6 +2261,102 @@
         <v>99</v>
       </c>
     </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B237" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="116">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>CMX-LaPaz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Hocaba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chopo.pdv</t>
   </si>
   <si>
     <t>CDMX005 / ANTONIO OMAR ROBLES FLORES</t>
@@ -384,10 +390,17 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -857,138 +870,141 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1516,7 +1532,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -1534,827 +1550,843 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B41" t="s">
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="A45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="A47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="A48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B49" t="s">
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" t="s">
+    <row r="51" spans="1:2">
+      <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="A52" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="A53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="A54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="A55" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="A56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>54</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="A58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="A59" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="A60" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="A61" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="A62" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="A63" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="A64" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>54</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="A65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>54</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="A66" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>54</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="A67" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>54</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="A68" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>54</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="A69" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>54</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="A70" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>54</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="A71" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>54</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="A72" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B73" t="s">
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" t="s">
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" t="s">
-        <v>79</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="A76" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" t="s">
-        <v>79</v>
-      </c>
-      <c r="B77" t="s">
+      <c r="A77" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>79</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="A78" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="A79" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="A80" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" t="s">
-        <v>79</v>
-      </c>
-      <c r="B81" t="s">
+      <c r="A81" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>79</v>
-      </c>
-      <c r="B82" t="s">
+      <c r="A82" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" t="s">
-        <v>79</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="A83" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" t="s">
-        <v>79</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="A84" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" t="s">
-        <v>79</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="A85" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>79</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="A86" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>79</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="A87" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>79</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="A88" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" t="s">
-        <v>79</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="A89" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" t="s">
-        <v>79</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="A90" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" t="s">
-        <v>79</v>
-      </c>
-      <c r="B91" t="s">
+      <c r="A91" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" t="s">
-        <v>79</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="A92" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B93" t="s">
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>100</v>
-      </c>
-      <c r="B94" t="s">
+    <row r="95" spans="1:2">
+      <c r="A95" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>100</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>100</v>
-      </c>
-      <c r="B96" t="s">
+      <c r="A96" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" t="s">
+      <c r="A97" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" t="s">
-        <v>100</v>
-      </c>
-      <c r="B98" t="s">
+      <c r="A98" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B99" t="s">
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>107</v>
-      </c>
-      <c r="B100" t="s">
+    <row r="101" spans="1:2">
+      <c r="A101" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>107</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>107</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="A102" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>107</v>
-      </c>
-      <c r="B103" t="s">
+      <c r="A103" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="A104" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -89,7 +89,7 @@
     <t>CMX-Cadiz.pdv</t>
   </si>
   <si>
-    <t>CDMX003 / LUIS ANDRE GALVAN PADILLA</t>
+    <t>CDMX003 / ALBERTO GONZALEZ SANCHEZ</t>
   </si>
   <si>
     <t>CMX-Hipodromo.pdv</t>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -89,7 +89,7 @@
     <t>CMX-Cadiz.pdv</t>
   </si>
   <si>
-    <t>CDMX003 / ALBERTO GONZALEZ SANCHEZ</t>
+    <t>CDMX003 / JOSE ENRIQUE RODRIGUEZ TAPIA</t>
   </si>
   <si>
     <t>CMX-Hipodromo.pdv</t>
@@ -113,7 +113,7 @@
     <t>CMX-Benavides.pdv</t>
   </si>
   <si>
-    <t>CDMX004 / JOSE LUIS AVILA PEREZ</t>
+    <t>CDMX004 / ALBERTO GONZALEZ SANCHEZ</t>
   </si>
   <si>
     <t>CMX-TorreBlanca.pdv</t>
@@ -1537,8 +1537,8 @@
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="26.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="26.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="42.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="26.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="42.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2390,9 +2390,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B237" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
     <t>CMX-Benavides.pdv</t>
   </si>
   <si>
-    <t>CDMX004 / ALBERTO GONZALEZ SANCHEZ</t>
+    <t>CDMX004 / JOSE LUIS AVILA PEREZ</t>
   </si>
   <si>
     <t>CMX-TorreBlanca.pdv</t>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="19635" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="158">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -62,10 +62,46 @@
     <t>CMX-LindaVista.pdv</t>
   </si>
   <si>
+    <t>CMX-Bolivar.pdv</t>
+  </si>
+  <si>
     <t>CMX-Naranjo.pdv</t>
   </si>
   <si>
-    <t>CMX-Bolivar.pdv</t>
+    <t>CMX-Romana.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Valenzuela.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Xalpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Rosario.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Linares.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Rayon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaViga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Remedios.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Palmira.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Coral.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pino.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Lavilla.pdv</t>
   </si>
   <si>
     <t>CDMX002 / ROBERTO CAMPOS ARENAS</t>
@@ -167,12 +203,30 @@
     <t>CMX-LaPaz.pdv</t>
   </si>
   <si>
+    <t>CMX-Cedros.pdv</t>
+  </si>
+  <si>
     <t>CMX-Hocaba.pdv</t>
   </si>
   <si>
     <t>CMX-Chopo.pdv</t>
   </si>
   <si>
+    <t>CMX-Aragon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Colipo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atitlan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aztecas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Galeana.pdV</t>
+  </si>
+  <si>
     <t>CDMX005 / ANTONIO OMAR ROBLES FLORES</t>
   </si>
   <si>
@@ -200,6 +254,9 @@
     <t>CMX-LaRosa.pdv</t>
   </si>
   <si>
+    <t>CMX-LasArmas.pd</t>
+  </si>
+  <si>
     <t>CDMX006 / LUCIA GUADALUPE JUAREZ DIAZ</t>
   </si>
   <si>
@@ -275,6 +332,51 @@
     <t>CMX-Lieja.pdv</t>
   </si>
   <si>
+    <t>CMX-Pirules.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gama.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sasatras.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tapiceria.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Independencia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Silao.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Circunvalacion.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atlixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arrieta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Dinares.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Caporales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Topacio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLuis.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tejada.pdv</t>
+  </si>
+  <si>
     <t>CDMX007 / ABEL ANTHONY ROSAS BENITEZ</t>
   </si>
   <si>
@@ -336,6 +438,30 @@
   </si>
   <si>
     <t>CMX-MilpaAlta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Fenix.pdy</t>
+  </si>
+  <si>
+    <t>CMX-Novelo.pdy</t>
+  </si>
+  <si>
+    <t>CMX-Avila.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepexpan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Juarez.pdv</t>
   </si>
   <si>
     <t>DIANA</t>
@@ -1532,7 +1658,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B148"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -1623,207 +1749,207 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>40</v>
@@ -1831,7 +1957,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>41</v>
@@ -1839,7 +1965,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>42</v>
@@ -1847,7 +1973,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>43</v>
@@ -1855,7 +1981,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>44</v>
@@ -1863,7 +1989,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>45</v>
@@ -1871,7 +1997,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>46</v>
@@ -1879,223 +2005,223 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>76</v>
@@ -2103,7 +2229,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>77</v>
@@ -2111,7 +2237,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
@@ -2119,7 +2245,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>79</v>
@@ -2127,7 +2253,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -2135,258 +2261,594 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="1" t="s">
         <v>115</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7620"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="161">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -227,6 +227,9 @@
     <t>CMX-Galeana.pdV</t>
   </si>
   <si>
+    <t>CMX-Aldama.pdv</t>
+  </si>
+  <si>
     <t>CDMX005 / ANTONIO OMAR ROBLES FLORES</t>
   </si>
   <si>
@@ -467,6 +470,9 @@
     <t>DIANA</t>
   </si>
   <si>
+    <t>CMX-Fenix.pdv</t>
+  </si>
+  <si>
     <t>CMX-Centro.pdv</t>
   </si>
   <si>
@@ -483,6 +489,9 @@
   </si>
   <si>
     <t>IXS-IxtapanSal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vizcainas.pdv</t>
   </si>
   <si>
     <t>SABINA</t>
@@ -511,10 +520,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -984,16 +993,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1658,13 +1667,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B148"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:B151"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="26.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="26.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="42.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="26.4259259259259" customWidth="1"/>
+    <col min="5" max="5" width="26.4259259259259" customWidth="1"/>
+    <col min="6" max="6" width="42.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2149,15 +2158,15 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>67</v>
@@ -2165,7 +2174,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>68</v>
@@ -2173,7 +2182,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>69</v>
@@ -2181,7 +2190,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>70</v>
@@ -2189,7 +2198,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>71</v>
@@ -2197,7 +2206,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>72</v>
@@ -2205,7 +2214,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>73</v>
@@ -2213,7 +2222,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>74</v>
@@ -2221,15 +2230,15 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>77</v>
@@ -2237,7 +2246,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
@@ -2245,7 +2254,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>79</v>
@@ -2253,7 +2262,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -2261,7 +2270,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>81</v>
@@ -2269,7 +2278,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
@@ -2277,7 +2286,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>83</v>
@@ -2285,7 +2294,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>84</v>
@@ -2293,7 +2302,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>85</v>
@@ -2301,7 +2310,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>86</v>
@@ -2309,7 +2318,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -2317,7 +2326,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>88</v>
@@ -2325,7 +2334,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>89</v>
@@ -2333,7 +2342,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>90</v>
@@ -2341,7 +2350,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>91</v>
@@ -2349,7 +2358,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -2357,7 +2366,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>93</v>
@@ -2365,7 +2374,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>94</v>
@@ -2373,7 +2382,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>95</v>
@@ -2381,7 +2390,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>96</v>
@@ -2389,7 +2398,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>97</v>
@@ -2397,7 +2406,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>98</v>
@@ -2405,7 +2414,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>99</v>
@@ -2413,7 +2422,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>100</v>
@@ -2421,7 +2430,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>101</v>
@@ -2429,7 +2438,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>102</v>
@@ -2437,7 +2446,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>103</v>
@@ -2445,7 +2454,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>104</v>
@@ -2453,7 +2462,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>105</v>
@@ -2461,7 +2470,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
@@ -2469,7 +2478,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>107</v>
@@ -2477,7 +2486,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>108</v>
@@ -2485,7 +2494,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>109</v>
@@ -2493,7 +2502,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>110</v>
@@ -2501,7 +2510,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>111</v>
@@ -2509,7 +2518,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>112</v>
@@ -2517,7 +2526,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>113</v>
@@ -2525,7 +2534,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>114</v>
@@ -2533,15 +2542,15 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>117</v>
@@ -2549,7 +2558,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>118</v>
@@ -2557,7 +2566,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>119</v>
@@ -2565,7 +2574,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>120</v>
@@ -2573,7 +2582,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>121</v>
@@ -2581,7 +2590,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>122</v>
@@ -2589,7 +2598,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>123</v>
@@ -2597,7 +2606,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>124</v>
@@ -2605,7 +2614,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>125</v>
@@ -2613,7 +2622,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>126</v>
@@ -2621,7 +2630,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>127</v>
@@ -2629,7 +2638,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>128</v>
@@ -2637,7 +2646,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>129</v>
@@ -2645,7 +2654,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>130</v>
@@ -2653,7 +2662,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>131</v>
@@ -2661,7 +2670,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>132</v>
@@ -2669,7 +2678,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>133</v>
@@ -2677,7 +2686,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>134</v>
@@ -2685,7 +2694,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>135</v>
@@ -2693,7 +2702,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>136</v>
@@ -2701,7 +2710,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>137</v>
@@ -2709,7 +2718,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>138</v>
@@ -2717,7 +2726,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>139</v>
@@ -2725,7 +2734,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>140</v>
@@ -2733,7 +2742,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>141</v>
@@ -2741,7 +2750,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>142</v>
@@ -2749,7 +2758,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>143</v>
@@ -2757,15 +2766,15 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>146</v>
@@ -2773,7 +2782,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>147</v>
@@ -2781,7 +2790,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>148</v>
@@ -2789,7 +2798,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>149</v>
@@ -2797,7 +2806,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>150</v>
@@ -2805,31 +2814,31 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>145</v>
+      </c>
+      <c r="B145" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>155</v>
@@ -2837,7 +2846,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>156</v>
@@ -2845,10 +2854,34 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>154</v>
+      </c>
+      <c r="B150" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="168">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -41,478 +41,499 @@
     <t>CDMX001 / JOSE ENRIQUE RODRIGUEZ TAPIA</t>
   </si>
   <si>
+    <t>CMX-Comonfort.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Hipodromo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LindaVista.pdv</t>
+  </si>
+  <si>
+    <t>CMX-MargaritaMaz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pantaco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanMarcos.pdv</t>
+  </si>
+  <si>
     <t>CMX-Tezozomoc.pdv</t>
   </si>
   <si>
-    <t>CMX-Comonfort.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanMarcos.pdv</t>
-  </si>
-  <si>
     <t>CMX-Victoria.pdv</t>
   </si>
   <si>
-    <t>CMX-Pantaco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-MargaritaMaz.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LindaVista.pdv</t>
+    <t>CMX-Benavides.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Naranjo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Xalpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Romana.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Coral.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pino.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaVilla.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Rosario.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Valenzuela.pdv</t>
+  </si>
+  <si>
+    <t>CDMX002 / ROBERTO CAMPOS ARENAS</t>
+  </si>
+  <si>
+    <t>CMX-Bondojito.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanJuan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepeyac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Triunfo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-VillaHermosa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Cadiz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Remedios.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Rayon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaViga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Palmira.pdv</t>
+  </si>
+  <si>
+    <t>CDMX003 / ENRIQUE ROMERO</t>
+  </si>
+  <si>
+    <t>CMX-Guerrero.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Obrera.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Roma.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Trebol.pdv</t>
+  </si>
+  <si>
+    <t>CMX-NuevoVallejo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Linares.pdv</t>
   </si>
   <si>
     <t>CMX-Bolivar.pdv</t>
   </si>
   <si>
-    <t>CMX-Naranjo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Romana.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Valenzuela.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Xalpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Rosario.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Linares.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Rayon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaViga.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Remedios.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Palmira.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Coral.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pino.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Lavilla.pdv</t>
-  </si>
-  <si>
-    <t>CDMX002 / ROBERTO CAMPOS ARENAS</t>
-  </si>
-  <si>
-    <t>CMX-Triunfo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-VillaHermosa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepeyac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Bondojito.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanJuan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Cadiz.pdv</t>
-  </si>
-  <si>
-    <t>CDMX003 / JOSE ENRIQUE RODRIGUEZ TAPIA</t>
-  </si>
-  <si>
-    <t>CMX-Hipodromo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Guerrero.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Trebol.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Roma.pdv</t>
-  </si>
-  <si>
-    <t>CMX-NuevoVallejo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Obrera.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Benavides.pdv</t>
-  </si>
-  <si>
     <t>CDMX004 / JOSE LUIS AVILA PEREZ</t>
   </si>
   <si>
+    <t>CMX-Barranca.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Cuajimalpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Encinos.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Guajiras.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Jalalpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LasAguilas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Loma.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixcoac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Olivar.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaPaz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aragon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Hocaba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Cedros.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aztecas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Galeana.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atacama.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aldama.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Amores.pdv</t>
+  </si>
+  <si>
+    <t>CDMX005 / ANTONIO OMAR ROBLES FLORES</t>
+  </si>
+  <si>
+    <t>CMX-Alamos.pdv</t>
+  </si>
+  <si>
+    <t>CMX-DelValle.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Division.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Napoles.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pestalozzi.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Portales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaCruz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Ixcateopan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaRosa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LasArmas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SalinaCruz.pdv</t>
+  </si>
+  <si>
+    <t>CDMX006 / LUCIA GUADALUPE JUAREZ DIAZ</t>
+  </si>
+  <si>
+    <t>CMX-AgricolaOriental.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaTraviata.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Leyes.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Magdalena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Palmitas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Polvorilla.pdv</t>
+  </si>
+  <si>
+    <t>CMX-RomeroRubio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLorenzo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaIsabel.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Santiago.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepalcates.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Torres.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vergel.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vulcanizacion.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Zapata.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Lieja.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepito.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Ayala.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atlixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Circunvalación.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pirules.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Silao.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Caporales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Topacio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gama.pdv</t>
+  </si>
+  <si>
+    <t>CDMX007 / ABEL ANTHONY ROSAS BENITEZ</t>
+  </si>
+  <si>
+    <t>CMX-Acoxpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arboledas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Catarina.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Culhuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Florida.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gardenia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Michoacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-MilpaAlta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Noria.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Padierna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pedregal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pegaso.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanAndres.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanPedro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaAna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantoDomingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tulyehualco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Xotepingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Peñon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanJeronimo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Becal.pdv</t>
+  </si>
+  <si>
+    <t>XLA-Xala.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Independencia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Avila.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Fenix.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Novelo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepexpan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Juarez.pdv</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>CMX-Centro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chile.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Union.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Uruguay.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vallejo.pdv</t>
+  </si>
+  <si>
+    <t>IXS-IxtapanSal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vizcainas.pdv</t>
+  </si>
+  <si>
+    <t>SABINA</t>
+  </si>
+  <si>
+    <t>ARR-Arriaga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Alva.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Argentina.pdvc</t>
+  </si>
+  <si>
+    <t>CMX-Cuba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Febrero.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Popotla.pdv</t>
+  </si>
+  <si>
+    <t>CDMX009 / REBECA GUDIÑO</t>
+  </si>
+  <si>
+    <t>CMX-Aztahuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Balbuena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Playa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlacotal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Villa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Zaragoza.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Dinares.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tapicería.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tejada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLuis.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arrieta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sasatras.pdv</t>
+  </si>
+  <si>
+    <t>CDMX010 / ALBERTO GONZALEZ</t>
+  </si>
+  <si>
+    <t>CMX-Anahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chapu.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Constituyentes.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Molino.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Polanco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Reforma.pdv</t>
+  </si>
+  <si>
     <t>CMX-TorreBlanca.pdv</t>
   </si>
   <si>
-    <t>CMX-Anahuac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Reforma.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Chapu.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Polanco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Constituyentes.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Molino.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Jalalpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Mixcoac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Guajiras.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LasAguilas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Olivar.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Encinos.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Barranca.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Cuajimalpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Loma.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaPaz.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Cedros.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Hocaba.pdv</t>
+    <t>CMX-Colipo.pdv</t>
   </si>
   <si>
     <t>CMX-Chopo.pdv</t>
   </si>
   <si>
-    <t>CMX-Aragon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Colipo.pdv</t>
-  </si>
-  <si>
     <t>CMX-Atitlan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Aztecas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Galeana.pdV</t>
-  </si>
-  <si>
-    <t>CMX-Aldama.pdv</t>
-  </si>
-  <si>
-    <t>CDMX005 / ANTONIO OMAR ROBLES FLORES</t>
-  </si>
-  <si>
-    <t>CMX-Napoles.pdv</t>
-  </si>
-  <si>
-    <t>CMX-DelValle.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pestalozzi.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaCruz.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Alamos.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Division.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Portales.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaRosa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LasArmas.pd</t>
-  </si>
-  <si>
-    <t>CDMX006 / LUCIA GUADALUPE JUAREZ DIAZ</t>
-  </si>
-  <si>
-    <t>CMX-Vulcanizacion.pdv</t>
-  </si>
-  <si>
-    <t>CMX-RomeroRubio.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Playa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Zaragoza.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Balbuena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepito.pdv</t>
-  </si>
-  <si>
-    <t>CMX-AgricolaOriental.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Zapata.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlacotal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Magdalena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Polvorilla.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaIsabel.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Palmitas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Leyes.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepalcates.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Aztahuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Ayala.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaTraviata.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Torres.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vergel.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanLorenzo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Villa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Santiago.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Lieja.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pirules.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gama.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sasatras.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tapiceria.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Independencia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Silao.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Circunvalacion.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Atlixco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arrieta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Dinares.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Caporales.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Topacio.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanLuis.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tejada.pdv</t>
-  </si>
-  <si>
-    <t>CDMX007 / ABEL ANTHONY ROSAS BENITEZ</t>
-  </si>
-  <si>
-    <t>CMX-Catarina.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Florida.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pegaso.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Xotepingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaAna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantoDomingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pedregal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Culhuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Padierna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Peñon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Michoacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Acoxpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arboledas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gardenia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanJeronimo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanPedro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanAndres.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Noria.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tulyehualco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-MilpaAlta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlahuac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Fenix.pdy</t>
-  </si>
-  <si>
-    <t>CMX-Novelo.pdy</t>
-  </si>
-  <si>
-    <t>CMX-Avila.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vada.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepexpan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Mixco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Juarez.pdv</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>CMX-Fenix.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Centro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Chile.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Union.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Uruguay.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vallejo.pdv</t>
-  </si>
-  <si>
-    <t>IXS-IxtapanSal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vizcainas.pdv</t>
-  </si>
-  <si>
-    <t>SABINA</t>
-  </si>
-  <si>
-    <t>ARR-Arriaga.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Alva.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Argentina.pdvc</t>
-  </si>
-  <si>
-    <t>CMX-Cuba.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Febrero.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Popotla.pdv</t>
   </si>
 </sst>
 </file>
@@ -1667,7 +1688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -1822,39 +1843,39 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>25</v>
@@ -1862,7 +1883,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>26</v>
@@ -1870,7 +1891,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>27</v>
@@ -1878,7 +1899,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>28</v>
@@ -1886,7 +1907,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>29</v>
@@ -1894,7 +1915,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
@@ -2102,71 +2123,71 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>67</v>
@@ -2174,7 +2195,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>68</v>
@@ -2182,7 +2203,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>69</v>
@@ -2190,55 +2211,55 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>77</v>
@@ -2246,7 +2267,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
@@ -2254,7 +2275,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>79</v>
@@ -2262,7 +2283,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -2270,7 +2291,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>81</v>
@@ -2278,7 +2299,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
@@ -2286,7 +2307,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>83</v>
@@ -2294,7 +2315,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>84</v>
@@ -2302,7 +2323,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>85</v>
@@ -2310,7 +2331,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>86</v>
@@ -2318,7 +2339,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -2326,7 +2347,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>88</v>
@@ -2334,7 +2355,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>89</v>
@@ -2342,7 +2363,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>90</v>
@@ -2350,7 +2371,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>91</v>
@@ -2358,7 +2379,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -2366,7 +2387,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>93</v>
@@ -2374,7 +2395,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>94</v>
@@ -2382,7 +2403,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>95</v>
@@ -2390,167 +2411,167 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>117</v>
@@ -2558,7 +2579,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>118</v>
@@ -2566,7 +2587,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>119</v>
@@ -2574,7 +2595,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>120</v>
@@ -2582,7 +2603,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>121</v>
@@ -2590,7 +2611,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>122</v>
@@ -2598,7 +2619,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>123</v>
@@ -2606,7 +2627,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>124</v>
@@ -2614,7 +2635,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>125</v>
@@ -2622,7 +2643,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>126</v>
@@ -2630,7 +2651,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>127</v>
@@ -2638,250 +2659,290 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="1" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="1" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="1" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B151" t="s">
-        <v>160</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>157</v>
+      </c>
+      <c r="B152" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>157</v>
+      </c>
+      <c r="B153" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>157</v>
+      </c>
+      <c r="B155" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="167">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -384,9 +384,6 @@
   </si>
   <si>
     <t>CMX-Becal.pdv</t>
-  </si>
-  <si>
-    <t>XLA-Xala.pdv</t>
   </si>
   <si>
     <t>CMX-Independencia.pdv</t>
@@ -541,10 +538,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1014,16 +1011,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1688,7 +1685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -2651,15 +2648,15 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>129</v>
@@ -2667,7 +2664,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>130</v>
@@ -2675,7 +2672,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>131</v>
@@ -2683,7 +2680,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>132</v>
@@ -2691,7 +2688,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>133</v>
@@ -2699,7 +2696,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>134</v>
@@ -2707,15 +2704,15 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>137</v>
@@ -2723,7 +2720,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>138</v>
@@ -2731,7 +2728,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>139</v>
@@ -2739,7 +2736,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>140</v>
@@ -2747,7 +2744,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>141</v>
@@ -2755,15 +2752,15 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>144</v>
@@ -2771,7 +2768,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>145</v>
@@ -2779,7 +2776,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>146</v>
@@ -2787,7 +2784,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>147</v>
@@ -2795,7 +2792,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>148</v>
@@ -2803,7 +2800,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>149</v>
@@ -2811,7 +2808,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>150</v>
@@ -2819,7 +2816,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>151</v>
@@ -2827,7 +2824,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>152</v>
@@ -2835,39 +2832,39 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B144" s="1" t="s">
+      <c r="A144" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>143</v>
-      </c>
-      <c r="B145" t="s">
+      <c r="A145" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="1" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>158</v>
@@ -2875,23 +2872,23 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B149" s="1" t="s">
+      <c r="A149" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B150" t="s">
         <v>161</v>
@@ -2899,7 +2896,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B151" t="s">
         <v>162</v>
@@ -2907,7 +2904,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B152" t="s">
         <v>163</v>
@@ -2915,7 +2912,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B153" t="s">
         <v>164</v>
@@ -2923,7 +2920,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B154" t="s">
         <v>165</v>
@@ -2931,18 +2928,10 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B155" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>157</v>
-      </c>
-      <c r="B156" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES VISITAS.xlsx
+++ b/SUPERVISORES VISITAS.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="168">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -308,196 +308,199 @@
     <t>CMX-Pirules.pdv</t>
   </si>
   <si>
+    <t>CMX-Caporales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Topacio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gama.pdv</t>
+  </si>
+  <si>
+    <t>CDMX007 / ABEL ANTHONY ROSAS BENITEZ</t>
+  </si>
+  <si>
+    <t>CMX-Acoxpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arboledas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Catarina.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Culhuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Florida.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gardenia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Michoacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-MilpaAlta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Noria.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Padierna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pedregal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pegaso.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanAndres.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanPedro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaAna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantoDomingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tulyehualco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Xotepingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Peñon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanJeronimo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Becal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Independencia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Avila.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Fenix.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Novelo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepexpan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Juarez.pdv</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>CMX-Centro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chile.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Union.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Uruguay.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vallejo.pdv</t>
+  </si>
+  <si>
+    <t>IXS-IxtapanSal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vizcainas.pdv</t>
+  </si>
+  <si>
+    <t>SABINA</t>
+  </si>
+  <si>
+    <t>ARR-Arriaga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Alva.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Argentina.pdvc</t>
+  </si>
+  <si>
+    <t>CMX-Cuba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Febrero.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Popotla.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Nacionales.pdv</t>
+  </si>
+  <si>
+    <t>CDMX009 / REBECA GUDIÑO</t>
+  </si>
+  <si>
+    <t>CMX-Aztahuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Balbuena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Playa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlacotal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Villa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Zaragoza.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Dinares.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tapicería.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tejada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLuis.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arrieta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sasatras.pdv</t>
+  </si>
+  <si>
     <t>CMX-Silao.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Caporales.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Topacio.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gama.pdv</t>
-  </si>
-  <si>
-    <t>CDMX007 / ABEL ANTHONY ROSAS BENITEZ</t>
-  </si>
-  <si>
-    <t>CMX-Acoxpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arboledas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Catarina.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Culhuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Florida.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gardenia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Michoacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-MilpaAlta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Noria.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Padierna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pedregal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pegaso.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanAndres.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanPedro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaAna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantoDomingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tulyehualco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Xotepingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Peñon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanJeronimo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Becal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Independencia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vada.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Avila.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Fenix.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlahuac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Novelo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepexpan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Mixco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Juarez.pdv</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>CMX-Centro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Chile.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Union.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Uruguay.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vallejo.pdv</t>
-  </si>
-  <si>
-    <t>IXS-IxtapanSal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vizcainas.pdv</t>
-  </si>
-  <si>
-    <t>SABINA</t>
-  </si>
-  <si>
-    <t>ARR-Arriaga.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Alva.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Argentina.pdvc</t>
-  </si>
-  <si>
-    <t>CMX-Cuba.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Febrero.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Popotla.pdv</t>
-  </si>
-  <si>
-    <t>CDMX009 / REBECA GUDIÑO</t>
-  </si>
-  <si>
-    <t>CMX-Aztahuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Balbuena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Playa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlacotal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Villa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Zaragoza.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Dinares.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tapicería.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tejada.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanLuis.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arrieta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sasatras.pdv</t>
   </si>
   <si>
     <t>CDMX010 / ALBERTO GONZALEZ</t>
@@ -1685,7 +1688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -2400,15 +2403,15 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>97</v>
@@ -2416,7 +2419,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>98</v>
@@ -2424,7 +2427,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>99</v>
@@ -2432,7 +2435,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>100</v>
@@ -2440,7 +2443,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>101</v>
@@ -2448,7 +2451,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>102</v>
@@ -2456,7 +2459,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>103</v>
@@ -2464,7 +2467,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>104</v>
@@ -2472,7 +2475,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>105</v>
@@ -2480,7 +2483,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
@@ -2488,7 +2491,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>107</v>
@@ -2496,7 +2499,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>108</v>
@@ -2504,7 +2507,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>109</v>
@@ -2512,7 +2515,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>110</v>
@@ -2520,7 +2523,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>111</v>
@@ -2528,7 +2531,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>112</v>
@@ -2536,7 +2539,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>113</v>
@@ -2544,7 +2547,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>114</v>
@@ -2552,7 +2555,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>115</v>
@@ -2560,7 +2563,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>116</v>
@@ -2568,7 +2571,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>117</v>
@@ -2576,7 +2579,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>118</v>
@@ -2584,7 +2587,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>119</v>
@@ -2592,7 +2595,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>120</v>
@@ -2600,7 +2603,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>121</v>
@@ -2608,7 +2611,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>122</v>
@@ -2616,7 +2619,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>123</v>
@@ -2624,7 +2627,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>124</v>
@@ -2632,7 +2635,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>125</v>
@@ -2640,15 +2643,15 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="1" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>128</v>
@@ -2656,7 +2659,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>129</v>
@@ -2664,7 +2667,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>130</v>
@@ -2672,7 +2675,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>131</v>
@@ -2680,7 +2683,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>132</v>
@@ -2688,7 +2691,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>133</v>
@@ -2696,15 +2699,15 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>136</v>
@@ -2712,7 +2715,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>137</v>
@@ -2720,7 +2723,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>138</v>
@@ -2728,7 +2731,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>139</v>
@@ -2736,7 +2739,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>140</v>
@@ -2744,7 +2747,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>141</v>
@@ -2856,15 +2859,15 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>158</v>
@@ -2872,7 +2875,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>159</v>
@@ -2880,7 +2883,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B149" t="s">
         <v>160</v>
@@ -2888,7 +2891,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B150" t="s">
         <v>161</v>
@@ -2896,7 +2899,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B151" t="s">
         <v>162</v>
@@ -2904,7 +2907,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B152" t="s">
         <v>163</v>
@@ -2912,7 +2915,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B153" t="s">
         <v>164</v>
@@ -2920,7 +2923,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B154" t="s">
         <v>165</v>
@@ -2928,10 +2931,18 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B155" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
